--- a/incident_report_forms/030_crowdstrike_incident_response_form--incident_report_forms.xlsx
+++ b/incident_report_forms/030_crowdstrike_incident_response_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phishing'}</t>
+          <t>phishing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phishing'}</t>
+          <t>Phishing</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'malware'}</t>
+          <t>malware</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Malware'}</t>
+          <t>Malware</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ransomware'}</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Ransomware'}</t>
+          <t>Ransomware</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phishing'}</t>
+          <t>phishing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phishing'}</t>
+          <t>Phishing</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'malware'}</t>
+          <t>malware</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Malware'}</t>
+          <t>Malware</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ransomware'}</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Ransomware'}</t>
+          <t>Ransomware</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'internal'}</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Internal'}</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'external'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'External'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'human_error'}</t>
+          <t>human_error</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Human Error'}</t>
+          <t>Human Error</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'technical_error'}</t>
+          <t>technical_error</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Technical Error'}</t>
+          <t>Technical Error</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_approved'}</t>
+          <t>not_approved</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Approved'}</t>
+          <t>Not Approved</t>
         </is>
       </c>
     </row>
